--- a/incident_report_forms/039_cybersecurity_incident_discharge_form--incident_report_forms.xlsx
+++ b/incident_report_forms/039_cybersecurity_incident_discharge_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'malware'}</t>
+          <t>malware</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Malware'}</t>
+          <t>Malware</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phishing'}</t>
+          <t>phishing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phishing'}</t>
+          <t>Phishing</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ransomware'}</t>
+          <t>ransomware</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Ransomware'}</t>
+          <t>Ransomware</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'human'}</t>
+          <t>human</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Human'}</t>
+          <t>Human</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nation-state'}</t>
+          <t>nation-state</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Nation-state'}</t>
+          <t>Nation-state</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'computer_network'}</t>
+          <t>computer_network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Computer Network'}</t>
+          <t>Computer Network</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'data'}</t>
+          <t>data</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Data'}</t>
+          <t>Data</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'hardware'}</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Hardware'}</t>
+          <t>Hardware</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'personnel'}</t>
+          <t>personnel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Personnel'}</t>
+          <t>Personnel</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
